--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1-ballot</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:14:00+00:00</t>
+    <t>2024-03-29T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:28:39+00:00</t>
+    <t>2024-04-02T09:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:17:05+00:00</t>
+    <t>2024-04-02T09:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:24:51+00:00</t>
+    <t>2024-04-02T09:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:46:01+00:00</t>
+    <t>2024-04-02T14:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:06:21+00:00</t>
+    <t>2024-04-02T14:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T09:39:19+00:00</t>
+    <t>2024-06-10T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T12:17:15+00:00</t>
+    <t>2024-06-11T12:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:10:45+00:00</t>
+    <t>2024-06-11T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:11:06+00:00</t>
+    <t>2024-06-14T08:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:12:27+00:00</t>
+    <t>2024-06-14T08:15:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:15:01+00:00</t>
+    <t>2024-06-19T07:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4858" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4858" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-19T07:50:19+00:00</t>
+    <t>2024-06-20T09:03:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1324,7 +1324,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1844,10 +1844,6 @@
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
-</t>
   </si>
   <si>
     <t>Référence vers la ressource Patient titulaire du dossier.</t>
@@ -17308,13 +17304,13 @@
         <v>75</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O143" t="s" s="2">
         <v>418</v>
@@ -17387,10 +17383,10 @@
         <v>307</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -17413,16 +17409,16 @@
         <v>75</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -17472,7 +17468,7 @@
         <v>75</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>76</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-20T09:03:18+00:00</t>
+    <t>2024-06-26T16:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T16:31:19+00:00</t>
+    <t>2024-07-24T15:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T15:57:10+00:00</t>
+    <t>2024-07-25T10:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T10:14:34+00:00</t>
+    <t>2024-07-31T08:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4858" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4832" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T08:54:42+00:00</t>
+    <t>2024-09-06T13:26:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -259,8 +259,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>Bundle.id</t>
@@ -302,10 +302,6 @@
   </si>
   <si>
     <t>Resource.meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -438,8 +434,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-1</t>
+    <t xml:space="preserve">bdl-1
+</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -496,16 +492,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -542,9 +528,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -552,9 +535,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -573,8 +553,11 @@
     <t>Slicing based on the profile conformance of the entry</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>open</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -632,8 +615,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -689,8 +672,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -744,9 +727,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -774,8 +754,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1001,7 +981,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.id</t>
@@ -1014,6 +994,13 @@
   </si>
   <si>
     <t>DocumentReference.meta.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>DocumentReference.meta.versionId</t>
@@ -1334,13 +1321,6 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>DocumentReference.date</t>
   </si>
   <si>
@@ -1521,13 +1501,6 @@
   </si>
   <si>
     <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
-  </si>
-  <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.id</t>
@@ -1795,14 +1768,6 @@
     <t>The time period over which the service that is described by the document was provided.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
@@ -1810,9 +1775,6 @@
   </si>
   <si>
     <t>The kind of facility where the patient was seen.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS</t>
@@ -2181,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24">
@@ -2189,7 +2151,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25">
@@ -2205,7 +2167,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27">
@@ -2213,7 +2175,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28">
@@ -2267,7 +2229,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35">
@@ -2303,7 +2265,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
@@ -2311,7 +2273,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41">
@@ -2795,10 +2757,10 @@
         <v>83</v>
       </c>
       <c r="AJ4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -2806,10 +2768,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
@@ -2832,16 +2794,16 @@
         <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" t="s" s="2">
+      <c r="O5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
@@ -2891,7 +2853,7 @@
         <v>75</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>76</v>
@@ -2900,10 +2862,10 @@
         <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -2911,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
@@ -2937,16 +2899,16 @@
         <v>75</v>
       </c>
       <c r="L6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="N6" t="s" s="2">
+      <c r="O6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
@@ -2972,32 +2934,32 @@
         <v>75</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Z6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AA6" t="s" s="2">
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AH6" t="s" s="2">
         <v>76</v>
       </c>
@@ -3005,10 +2967,10 @@
         <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -3016,10 +2978,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
@@ -3042,16 +3004,16 @@
         <v>84</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="N7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" t="s" s="2">
@@ -3101,7 +3063,7 @@
         <v>75</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>76</v>
@@ -3110,10 +3072,10 @@
         <v>83</v>
       </c>
       <c r="AJ7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -3121,10 +3083,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -3147,16 +3109,16 @@
         <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M8" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="N8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" t="s" s="2">
@@ -3167,29 +3129,29 @@
         <v>75</v>
       </c>
       <c r="T8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="U8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="Z8" t="s" s="2">
+      <c r="AA8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AA8" t="s" s="2">
-        <v>124</v>
-      </c>
       <c r="AB8" t="s" s="2">
         <v>75</v>
       </c>
@@ -3206,7 +3168,7 @@
         <v>75</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>83</v>
@@ -3215,10 +3177,10 @@
         <v>83</v>
       </c>
       <c r="AJ8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -3226,10 +3188,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -3252,16 +3214,16 @@
         <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="N9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" t="s" s="2">
@@ -3311,7 +3273,7 @@
         <v>75</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>76</v>
@@ -3320,10 +3282,10 @@
         <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK9" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -3331,10 +3293,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -3357,16 +3319,16 @@
         <v>84</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="N10" t="s" s="2">
+      <c r="O10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" t="s" s="2">
@@ -3416,7 +3378,7 @@
         <v>75</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>76</v>
@@ -3425,10 +3387,10 @@
         <v>83</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -3436,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -3462,16 +3424,16 @@
         <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" t="s" s="2">
@@ -3521,7 +3483,7 @@
         <v>75</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>76</v>
@@ -3530,10 +3492,10 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -3541,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3567,13 +3529,13 @@
         <v>75</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -3624,7 +3586,7 @@
         <v>75</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>76</v>
@@ -3644,14 +3606,14 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" t="s" s="2">
@@ -3670,16 +3632,16 @@
         <v>75</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
@@ -3717,19 +3679,19 @@
         <v>75</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>76</v>
@@ -3738,10 +3700,10 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
@@ -3749,14 +3711,14 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
@@ -3775,19 +3737,19 @@
         <v>84</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q14" t="s" s="2">
         <v>75</v>
@@ -3836,7 +3798,7 @@
         <v>75</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>76</v>
@@ -3845,10 +3807,10 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
@@ -3856,10 +3818,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3882,17 +3844,15 @@
         <v>84</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" t="s" s="2">
         <v>75</v>
@@ -3941,7 +3901,7 @@
         <v>75</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>83</v>
@@ -3950,10 +3910,10 @@
         <v>83</v>
       </c>
       <c r="AJ15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -3961,10 +3921,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3987,17 +3947,15 @@
         <v>84</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
         <v>75</v>
@@ -4046,7 +4004,7 @@
         <v>75</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>83</v>
@@ -4055,10 +4013,10 @@
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="17">
@@ -4066,10 +4024,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -4092,13 +4050,13 @@
         <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -4137,19 +4095,19 @@
         <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AE17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>76</v>
@@ -4158,10 +4116,10 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
@@ -4169,10 +4127,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -4195,13 +4153,13 @@
         <v>75</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -4252,7 +4210,7 @@
         <v>75</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>76</v>
@@ -4272,14 +4230,14 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
@@ -4298,16 +4256,16 @@
         <v>75</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
@@ -4345,19 +4303,19 @@
         <v>75</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>76</v>
@@ -4366,10 +4324,10 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
@@ -4377,14 +4335,14 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" t="s" s="2">
@@ -4403,19 +4361,19 @@
         <v>84</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q20" t="s" s="2">
         <v>75</v>
@@ -4464,7 +4422,7 @@
         <v>75</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
@@ -4473,10 +4431,10 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -4484,10 +4442,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4513,10 +4471,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -4567,7 +4525,7 @@
         <v>75</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
@@ -4579,7 +4537,7 @@
         <v>75</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
@@ -4587,10 +4545,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4613,16 +4571,16 @@
         <v>84</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
@@ -4672,7 +4630,7 @@
         <v>75</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -4681,10 +4639,10 @@
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -4692,10 +4650,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4718,13 +4676,13 @@
         <v>84</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -4775,7 +4733,7 @@
         <v>75</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
@@ -4795,10 +4753,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4821,13 +4779,13 @@
         <v>84</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -4878,7 +4836,7 @@
         <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -4887,10 +4845,10 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -4898,10 +4856,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4924,13 +4882,13 @@
         <v>75</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -4981,7 +4939,7 @@
         <v>75</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>76</v>
@@ -5001,14 +4959,14 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
@@ -5027,16 +4985,16 @@
         <v>75</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
@@ -5074,19 +5032,19 @@
         <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
@@ -5095,10 +5053,10 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
@@ -5106,14 +5064,14 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
@@ -5132,19 +5090,19 @@
         <v>84</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>75</v>
@@ -5193,7 +5151,7 @@
         <v>75</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
@@ -5202,10 +5160,10 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28">
@@ -5213,10 +5171,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5239,16 +5197,16 @@
         <v>84</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
@@ -5274,13 +5232,13 @@
         <v>75</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AB28" t="s" s="2">
         <v>75</v>
@@ -5298,7 +5256,7 @@
         <v>75</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
@@ -5307,10 +5265,10 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -5318,10 +5276,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5344,16 +5302,16 @@
         <v>84</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
@@ -5403,7 +5361,7 @@
         <v>75</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5412,10 +5370,10 @@
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="30">
@@ -5423,10 +5381,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5449,13 +5407,13 @@
         <v>84</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -5506,7 +5464,7 @@
         <v>75</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -5515,10 +5473,10 @@
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
@@ -5526,10 +5484,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5552,13 +5510,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -5609,7 +5567,7 @@
         <v>75</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5629,14 +5587,14 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
@@ -5655,16 +5613,16 @@
         <v>75</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5702,19 +5660,19 @@
         <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -5723,10 +5681,10 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33">
@@ -5734,14 +5692,14 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
@@ -5760,19 +5718,19 @@
         <v>84</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q33" t="s" s="2">
         <v>75</v>
@@ -5821,7 +5779,7 @@
         <v>75</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
@@ -5830,10 +5788,10 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
@@ -5841,10 +5799,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5867,17 +5825,15 @@
         <v>84</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
         <v>75</v>
@@ -5902,13 +5858,13 @@
         <v>75</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AB34" t="s" s="2">
         <v>75</v>
@@ -5926,7 +5882,7 @@
         <v>75</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>83</v>
@@ -5935,10 +5891,10 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK34" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="35">
@@ -5946,10 +5902,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5972,16 +5928,16 @@
         <v>84</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
@@ -6031,7 +5987,7 @@
         <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>83</v>
@@ -6040,10 +5996,10 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="36">
@@ -6051,10 +6007,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6077,17 +6033,15 @@
         <v>84</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>75</v>
@@ -6136,7 +6090,7 @@
         <v>75</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
@@ -6145,10 +6099,10 @@
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK36" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="37">
@@ -6156,10 +6110,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6182,17 +6136,15 @@
         <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
         <v>75</v>
@@ -6241,7 +6193,7 @@
         <v>75</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
@@ -6250,10 +6202,10 @@
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="38">
@@ -6261,10 +6213,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6287,17 +6239,15 @@
         <v>84</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
         <v>75</v>
@@ -6346,7 +6296,7 @@
         <v>75</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6355,10 +6305,10 @@
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="39">
@@ -6366,10 +6316,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6392,17 +6342,15 @@
         <v>84</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
         <v>75</v>
@@ -6451,7 +6399,7 @@
         <v>75</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
@@ -6460,10 +6408,10 @@
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="40">
@@ -6471,10 +6419,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6497,13 +6445,13 @@
         <v>84</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -6554,7 +6502,7 @@
         <v>75</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -6563,10 +6511,10 @@
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
@@ -6574,10 +6522,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6600,13 +6548,13 @@
         <v>75</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -6657,7 +6605,7 @@
         <v>75</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -6677,14 +6625,14 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
@@ -6703,16 +6651,16 @@
         <v>75</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -6750,19 +6698,19 @@
         <v>75</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -6771,10 +6719,10 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43">
@@ -6782,14 +6730,14 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -6808,19 +6756,19 @@
         <v>84</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P43" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q43" t="s" s="2">
         <v>75</v>
@@ -6869,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -6878,10 +6826,10 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44">
@@ -6889,10 +6837,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6915,17 +6863,15 @@
         <v>84</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
         <v>75</v>
@@ -6974,7 +6920,7 @@
         <v>75</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>83</v>
@@ -6983,10 +6929,10 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="45">
@@ -6994,10 +6940,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7020,17 +6966,15 @@
         <v>84</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
         <v>75</v>
@@ -7079,7 +7023,7 @@
         <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -7088,10 +7032,10 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="46">
@@ -7099,10 +7043,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7125,16 +7069,16 @@
         <v>84</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7184,7 +7128,7 @@
         <v>75</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7193,10 +7137,10 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK46" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="47">
@@ -7204,10 +7148,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7230,16 +7174,16 @@
         <v>84</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7289,7 +7233,7 @@
         <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7298,10 +7242,10 @@
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="48">
@@ -7309,10 +7253,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7335,16 +7279,16 @@
         <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -7394,7 +7338,7 @@
         <v>75</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7414,13 +7358,13 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E49" t="s" s="2">
         <v>75</v>
@@ -7442,13 +7386,13 @@
         <v>84</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -7499,7 +7443,7 @@
         <v>75</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -7508,10 +7452,10 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50">
@@ -7519,10 +7463,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7545,13 +7489,13 @@
         <v>75</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
@@ -7602,7 +7546,7 @@
         <v>75</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -7622,14 +7566,14 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
@@ -7648,16 +7592,16 @@
         <v>75</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
@@ -7695,19 +7639,19 @@
         <v>75</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -7716,10 +7660,10 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52">
@@ -7727,14 +7671,14 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
@@ -7753,19 +7697,19 @@
         <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>75</v>
@@ -7814,7 +7758,7 @@
         <v>75</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
@@ -7823,10 +7767,10 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
@@ -7834,10 +7778,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7863,10 +7807,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -7917,7 +7861,7 @@
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -7929,7 +7873,7 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54">
@@ -7937,10 +7881,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7963,16 +7907,16 @@
         <v>84</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -8022,7 +7966,7 @@
         <v>75</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -8031,10 +7975,10 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="55">
@@ -8042,10 +7986,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8068,16 +8012,16 @@
         <v>75</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
@@ -8127,7 +8071,7 @@
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8147,10 +8091,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8173,13 +8117,13 @@
         <v>84</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -8230,7 +8174,7 @@
         <v>75</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -8239,10 +8183,10 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57">
@@ -8250,10 +8194,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8276,13 +8220,13 @@
         <v>75</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8333,7 +8277,7 @@
         <v>75</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -8353,14 +8297,14 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" t="s" s="2">
@@ -8379,16 +8323,16 @@
         <v>75</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -8426,19 +8370,19 @@
         <v>75</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
@@ -8447,10 +8391,10 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59">
@@ -8458,14 +8402,14 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -8484,19 +8428,19 @@
         <v>84</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P59" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>75</v>
@@ -8545,7 +8489,7 @@
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -8554,10 +8498,10 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60">
@@ -8565,10 +8509,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8591,16 +8535,16 @@
         <v>84</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8626,13 +8570,13 @@
         <v>75</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AA60" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AB60" t="s" s="2">
         <v>75</v>
@@ -8650,7 +8594,7 @@
         <v>75</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -8659,10 +8603,10 @@
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="61">
@@ -8670,10 +8614,10 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8696,16 +8640,16 @@
         <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8755,7 +8699,7 @@
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
@@ -8764,10 +8708,10 @@
         <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="62">
@@ -8775,10 +8719,10 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8801,13 +8745,13 @@
         <v>84</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8858,7 +8802,7 @@
         <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -8867,10 +8811,10 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63">
@@ -8878,10 +8822,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8904,13 +8848,13 @@
         <v>75</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
@@ -8961,7 +8905,7 @@
         <v>75</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
@@ -8981,14 +8925,14 @@
         <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" t="s" s="2">
@@ -9007,16 +8951,16 @@
         <v>75</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -9054,19 +8998,19 @@
         <v>75</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>76</v>
@@ -9075,10 +9019,10 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65">
@@ -9086,14 +9030,14 @@
         <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
@@ -9112,19 +9056,19 @@
         <v>84</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>75</v>
@@ -9173,7 +9117,7 @@
         <v>75</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>76</v>
@@ -9182,10 +9126,10 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66">
@@ -9193,10 +9137,10 @@
         <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9219,17 +9163,15 @@
         <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>75</v>
@@ -9239,7 +9181,7 @@
         <v>75</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>75</v>
@@ -9254,13 +9196,13 @@
         <v>75</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AB66" t="s" s="2">
         <v>75</v>
@@ -9278,7 +9220,7 @@
         <v>75</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>83</v>
@@ -9287,10 +9229,10 @@
         <v>83</v>
       </c>
       <c r="AJ66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="67">
@@ -9298,10 +9240,10 @@
         <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9324,16 +9266,16 @@
         <v>84</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9383,7 +9325,7 @@
         <v>75</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>83</v>
@@ -9392,10 +9334,10 @@
         <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK67" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="68">
@@ -9403,10 +9345,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9429,17 +9371,15 @@
         <v>84</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
         <v>75</v>
@@ -9488,7 +9428,7 @@
         <v>75</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>76</v>
@@ -9497,10 +9437,10 @@
         <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="69">
@@ -9508,10 +9448,10 @@
         <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9534,17 +9474,15 @@
         <v>84</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
         <v>75</v>
@@ -9593,7 +9531,7 @@
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -9602,10 +9540,10 @@
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK69" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="70">
@@ -9613,10 +9551,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9639,17 +9577,15 @@
         <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
         <v>75</v>
@@ -9698,7 +9634,7 @@
         <v>75</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9707,10 +9643,10 @@
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="71">
@@ -9718,10 +9654,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9744,17 +9680,15 @@
         <v>84</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
         <v>75</v>
@@ -9803,7 +9737,7 @@
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
@@ -9812,10 +9746,10 @@
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK71" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="72">
@@ -9823,10 +9757,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9849,13 +9783,13 @@
         <v>84</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -9906,7 +9840,7 @@
         <v>75</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>76</v>
@@ -9915,10 +9849,10 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73">
@@ -9926,10 +9860,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9952,13 +9886,13 @@
         <v>75</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
@@ -10009,7 +9943,7 @@
         <v>75</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -10029,14 +9963,14 @@
         <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
@@ -10055,16 +9989,16 @@
         <v>75</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -10102,19 +10036,19 @@
         <v>75</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD74" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
@@ -10123,10 +10057,10 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75">
@@ -10134,14 +10068,14 @@
         <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
@@ -10160,19 +10094,19 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P75" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>75</v>
@@ -10221,7 +10155,7 @@
         <v>75</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10230,10 +10164,10 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76">
@@ -10241,10 +10175,10 @@
         <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10267,17 +10201,15 @@
         <v>84</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
         <v>75</v>
@@ -10326,7 +10258,7 @@
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>83</v>
@@ -10335,10 +10267,10 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK76" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="77">
@@ -10346,10 +10278,10 @@
         <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10372,17 +10304,15 @@
         <v>84</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
         <v>75</v>
@@ -10431,7 +10361,7 @@
         <v>75</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10440,10 +10370,10 @@
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK77" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="78">
@@ -10451,10 +10381,10 @@
         <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10477,16 +10407,16 @@
         <v>84</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
@@ -10536,7 +10466,7 @@
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -10545,10 +10475,10 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK78" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -10556,10 +10486,10 @@
         <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10582,16 +10512,16 @@
         <v>84</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
@@ -10641,7 +10571,7 @@
         <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>76</v>
@@ -10650,10 +10580,10 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK79" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="80">
@@ -10661,10 +10591,10 @@
         <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10687,16 +10617,16 @@
         <v>84</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
@@ -10746,7 +10676,7 @@
         <v>75</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -10766,10 +10696,10 @@
         <v>3</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10792,19 +10722,19 @@
         <v>84</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>75</v>
@@ -10853,7 +10783,7 @@
         <v>75</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10862,21 +10792,21 @@
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK81" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10902,13 +10832,13 @@
         <v>78</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
@@ -10958,7 +10888,7 @@
         <v>75</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
@@ -10970,18 +10900,18 @@
         <v>75</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11080,13 +11010,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11175,21 +11105,21 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK84" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11212,13 +11142,13 @@
         <v>75</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -11269,7 +11199,7 @@
         <v>75</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11286,17 +11216,17 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
@@ -11315,16 +11245,16 @@
         <v>75</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
@@ -11362,19 +11292,19 @@
         <v>75</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>152</v>
+        <v>313</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>153</v>
+        <v>314</v>
       </c>
       <c r="AE86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11383,21 +11313,21 @@
         <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11423,13 +11353,13 @@
         <v>85</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
@@ -11479,7 +11409,7 @@
         <v>75</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -11488,21 +11418,21 @@
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK87" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11525,16 +11455,16 @@
         <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -11584,7 +11514,7 @@
         <v>75</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -11593,21 +11523,21 @@
         <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK88" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11630,16 +11560,16 @@
         <v>84</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -11689,7 +11619,7 @@
         <v>75</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -11698,21 +11628,21 @@
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK89" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11735,16 +11665,16 @@
         <v>84</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -11794,7 +11724,7 @@
         <v>75</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -11803,21 +11733,21 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK90" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11840,16 +11770,16 @@
         <v>84</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -11875,13 +11805,13 @@
         <v>75</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>75</v>
@@ -11899,7 +11829,7 @@
         <v>75</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -11908,21 +11838,21 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK91" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11945,16 +11875,16 @@
         <v>84</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
@@ -11980,13 +11910,13 @@
         <v>75</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>75</v>
@@ -12004,7 +11934,7 @@
         <v>75</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -12013,21 +11943,21 @@
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK92" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12050,16 +11980,16 @@
         <v>84</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
@@ -12109,7 +12039,7 @@
         <v>75</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12118,21 +12048,21 @@
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK93" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12155,16 +12085,16 @@
         <v>75</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
@@ -12190,32 +12120,32 @@
         <v>75</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Z94" t="s" s="2">
+      <c r="AA94" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AA94" t="s" s="2">
+      <c r="AB94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG94" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
       </c>
@@ -12223,25 +12153,25 @@
         <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK94" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
@@ -12260,16 +12190,16 @@
         <v>75</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="P95" s="2"/>
       <c r="Q95" t="s" s="2">
@@ -12319,7 +12249,7 @@
         <v>75</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
@@ -12328,25 +12258,25 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK95" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
@@ -12365,16 +12295,16 @@
         <v>75</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="P96" s="2"/>
       <c r="Q96" t="s" s="2">
@@ -12424,7 +12354,7 @@
         <v>75</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -12441,17 +12371,17 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
@@ -12470,16 +12400,16 @@
         <v>75</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="N97" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
@@ -12517,19 +12447,19 @@
         <v>75</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -12538,21 +12468,21 @@
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12575,13 +12505,13 @@
         <v>75</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -12620,19 +12550,19 @@
         <v>75</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD98" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>76</v>
@@ -12641,21 +12571,21 @@
         <v>77</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12678,19 +12608,19 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="P99" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="Q99" t="s" s="2">
         <v>75</v>
@@ -12739,7 +12669,7 @@
         <v>75</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -12748,21 +12678,21 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK99" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12785,13 +12715,13 @@
         <v>84</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -12842,7 +12772,7 @@
         <v>75</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -12851,21 +12781,21 @@
         <v>77</v>
       </c>
       <c r="AJ100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK100" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12888,16 +12818,16 @@
         <v>84</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
@@ -12908,7 +12838,7 @@
         <v>75</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>75</v>
@@ -12923,13 +12853,13 @@
         <v>75</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AB101" t="s" s="2">
         <v>75</v>
@@ -12947,7 +12877,7 @@
         <v>75</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>83</v>
@@ -12956,21 +12886,21 @@
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK101" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12993,16 +12923,16 @@
         <v>84</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="P102" s="2"/>
       <c r="Q102" t="s" s="2">
@@ -13028,13 +12958,13 @@
         <v>75</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>75</v>
@@ -13052,7 +12982,7 @@
         <v>75</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -13061,21 +12991,21 @@
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK102" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13098,16 +13028,16 @@
         <v>84</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -13133,11 +13063,11 @@
         <v>75</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>75</v>
@@ -13155,7 +13085,7 @@
         <v>75</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
@@ -13164,25 +13094,25 @@
         <v>83</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
@@ -13201,16 +13131,16 @@
         <v>84</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="P104" s="2"/>
       <c r="Q104" t="s" s="2">
@@ -13236,11 +13166,11 @@
         <v>75</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z104" s="2"/>
       <c r="AA104" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>75</v>
@@ -13258,7 +13188,7 @@
         <v>75</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>76</v>
@@ -13267,21 +13197,21 @@
         <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13304,17 +13234,15 @@
         <v>84</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" t="s" s="2">
         <v>75</v>
@@ -13363,7 +13291,7 @@
         <v>75</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
@@ -13372,25 +13300,25 @@
         <v>83</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK105" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -13409,16 +13337,16 @@
         <v>84</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13468,7 +13396,7 @@
         <v>75</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -13477,21 +13405,21 @@
         <v>83</v>
       </c>
       <c r="AJ106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK106" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13514,16 +13442,16 @@
         <v>84</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -13573,7 +13501,7 @@
         <v>75</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
@@ -13582,21 +13510,21 @@
         <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK107" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13619,16 +13547,16 @@
         <v>75</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -13678,7 +13606,7 @@
         <v>75</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -13687,21 +13615,21 @@
         <v>83</v>
       </c>
       <c r="AJ108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK108" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13724,16 +13652,16 @@
         <v>75</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -13783,7 +13711,7 @@
         <v>75</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>76</v>
@@ -13792,21 +13720,21 @@
         <v>83</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK109" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13829,16 +13757,16 @@
         <v>84</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
@@ -13888,7 +13816,7 @@
         <v>75</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -13897,21 +13825,21 @@
         <v>77</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK110" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -13934,13 +13862,13 @@
         <v>75</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -13991,7 +13919,7 @@
         <v>75</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -14008,17 +13936,17 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" t="s" s="2">
@@ -14037,16 +13965,16 @@
         <v>75</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14084,19 +14012,19 @@
         <v>75</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD112" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -14105,25 +14033,25 @@
         <v>77</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" t="s" s="2">
@@ -14142,19 +14070,19 @@
         <v>84</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P113" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q113" t="s" s="2">
         <v>75</v>
@@ -14203,7 +14131,7 @@
         <v>75</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>76</v>
@@ -14212,21 +14140,21 @@
         <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14249,16 +14177,16 @@
         <v>84</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="P114" s="2"/>
       <c r="Q114" t="s" s="2">
@@ -14284,13 +14212,13 @@
         <v>75</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AA114" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AB114" t="s" s="2">
         <v>75</v>
@@ -14308,7 +14236,7 @@
         <v>75</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>83</v>
@@ -14317,21 +14245,21 @@
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK114" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -14354,17 +14282,15 @@
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" s="2"/>
       <c r="Q115" t="s" s="2">
         <v>75</v>
@@ -14413,7 +14339,7 @@
         <v>75</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>83</v>
@@ -14422,21 +14348,21 @@
         <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK115" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14459,19 +14385,19 @@
         <v>84</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="P116" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>75</v>
@@ -14520,7 +14446,7 @@
         <v>75</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>76</v>
@@ -14529,21 +14455,21 @@
         <v>83</v>
       </c>
       <c r="AJ116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK116" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14566,19 +14492,19 @@
         <v>84</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="P117" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="Q117" t="s" s="2">
         <v>75</v>
@@ -14603,13 +14529,13 @@
         <v>75</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AA117" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AB117" t="s" s="2">
         <v>75</v>
@@ -14627,7 +14553,7 @@
         <v>75</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>76</v>
@@ -14636,21 +14562,21 @@
         <v>77</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -14673,13 +14599,13 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -14730,7 +14656,7 @@
         <v>75</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>83</v>
@@ -14739,21 +14665,21 @@
         <v>77</v>
       </c>
       <c r="AJ118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK118" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -14776,13 +14702,13 @@
         <v>75</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -14833,7 +14759,7 @@
         <v>75</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -14850,17 +14776,17 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" t="s" s="2">
@@ -14879,16 +14805,16 @@
         <v>75</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
@@ -14926,19 +14852,19 @@
         <v>75</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD120" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>76</v>
@@ -14947,25 +14873,25 @@
         <v>77</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" t="s" s="2">
@@ -14984,19 +14910,19 @@
         <v>84</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P121" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q121" t="s" s="2">
         <v>75</v>
@@ -15045,7 +14971,7 @@
         <v>75</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>76</v>
@@ -15054,21 +14980,21 @@
         <v>77</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -15091,17 +15017,15 @@
         <v>84</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
         <v>75</v>
@@ -15150,7 +15074,7 @@
         <v>75</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>83</v>
@@ -15159,21 +15083,21 @@
         <v>83</v>
       </c>
       <c r="AJ122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK122" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15196,13 +15120,13 @@
         <v>75</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -15253,7 +15177,7 @@
         <v>75</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -15270,17 +15194,17 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" t="s" s="2">
@@ -15299,16 +15223,16 @@
         <v>75</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
@@ -15346,19 +15270,19 @@
         <v>75</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>152</v>
+        <v>313</v>
       </c>
       <c r="AD124" t="s" s="2">
-        <v>153</v>
+        <v>314</v>
       </c>
       <c r="AE124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -15367,21 +15291,21 @@
         <v>77</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15404,19 +15328,17 @@
         <v>84</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="Q125" t="s" s="2">
         <v>75</v>
@@ -15429,7 +15351,7 @@
         <v>75</v>
       </c>
       <c r="U125" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="V125" t="s" s="2">
         <v>75</v>
@@ -15441,13 +15363,13 @@
         <v>75</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="AA125" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="AB125" t="s" s="2">
         <v>75</v>
@@ -15465,7 +15387,7 @@
         <v>75</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -15474,21 +15396,21 @@
         <v>83</v>
       </c>
       <c r="AJ125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK125" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15511,19 +15433,17 @@
         <v>84</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="Q126" t="s" s="2">
         <v>75</v>
@@ -15536,7 +15456,7 @@
         <v>75</v>
       </c>
       <c r="U126" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="V126" t="s" s="2">
         <v>75</v>
@@ -15548,14 +15468,14 @@
         <v>75</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AA126" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AA126" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="AB126" t="s" s="2">
         <v>75</v>
       </c>
@@ -15572,7 +15492,7 @@
         <v>75</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>76</v>
@@ -15581,21 +15501,21 @@
         <v>83</v>
       </c>
       <c r="AJ126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK126" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -15618,19 +15538,19 @@
         <v>75</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="P127" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="Q127" t="s" s="2">
         <v>75</v>
@@ -15679,7 +15599,7 @@
         <v>75</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -15688,21 +15608,21 @@
         <v>83</v>
       </c>
       <c r="AJ127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK127" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -15725,19 +15645,19 @@
         <v>84</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="P128" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>75</v>
@@ -15750,7 +15670,7 @@
         <v>75</v>
       </c>
       <c r="U128" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="V128" t="s" s="2">
         <v>75</v>
@@ -15786,7 +15706,7 @@
         <v>75</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
@@ -15795,21 +15715,21 @@
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK128" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -15832,19 +15752,19 @@
         <v>84</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="P129" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>75</v>
@@ -15893,7 +15813,7 @@
         <v>75</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -15902,21 +15822,21 @@
         <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK129" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -15939,19 +15859,19 @@
         <v>84</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="P130" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="Q130" t="s" s="2">
         <v>75</v>
@@ -16000,7 +15920,7 @@
         <v>75</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
@@ -16009,21 +15929,21 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK130" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16046,19 +15966,17 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>75</v>
@@ -16071,7 +15989,7 @@
         <v>75</v>
       </c>
       <c r="U131" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="V131" t="s" s="2">
         <v>75</v>
@@ -16107,7 +16025,7 @@
         <v>75</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -16116,21 +16034,21 @@
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK131" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16153,17 +16071,17 @@
         <v>84</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>75</v>
@@ -16212,7 +16130,7 @@
         <v>75</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
@@ -16221,21 +16139,21 @@
         <v>83</v>
       </c>
       <c r="AJ132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK132" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16258,16 +16176,16 @@
         <v>84</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -16293,11 +16211,11 @@
         <v>75</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z133" s="2"/>
       <c r="AA133" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AB133" t="s" s="2">
         <v>75</v>
@@ -16315,7 +16233,7 @@
         <v>75</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>76</v>
@@ -16324,21 +16242,21 @@
         <v>83</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -16361,16 +16279,16 @@
         <v>84</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -16420,7 +16338,7 @@
         <v>75</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>76</v>
@@ -16429,21 +16347,21 @@
         <v>83</v>
       </c>
       <c r="AJ134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK134" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -16466,13 +16384,13 @@
         <v>75</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -16523,7 +16441,7 @@
         <v>75</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>76</v>
@@ -16540,17 +16458,17 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" t="s" s="2">
@@ -16569,16 +16487,16 @@
         <v>75</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P136" s="2"/>
       <c r="Q136" t="s" s="2">
@@ -16616,19 +16534,19 @@
         <v>75</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AD136" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AE136" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -16637,25 +16555,25 @@
         <v>77</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
@@ -16674,19 +16592,19 @@
         <v>84</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P137" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q137" t="s" s="2">
         <v>75</v>
@@ -16735,7 +16653,7 @@
         <v>75</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>76</v>
@@ -16744,21 +16662,21 @@
         <v>77</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -16781,17 +16699,15 @@
         <v>75</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" s="2"/>
       <c r="Q138" t="s" s="2">
         <v>75</v>
@@ -16840,7 +16756,7 @@
         <v>75</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>76</v>
@@ -16849,21 +16765,21 @@
         <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK138" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -16886,16 +16802,16 @@
         <v>75</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
@@ -16921,13 +16837,13 @@
         <v>75</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="AA139" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="AB139" t="s" s="2">
         <v>75</v>
@@ -16945,7 +16861,7 @@
         <v>75</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>76</v>
@@ -16954,21 +16870,21 @@
         <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -16991,17 +16907,15 @@
         <v>84</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" s="2"/>
       <c r="Q140" t="s" s="2">
         <v>75</v>
@@ -17050,7 +16964,7 @@
         <v>75</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>76</v>
@@ -17059,21 +16973,21 @@
         <v>83</v>
       </c>
       <c r="AJ140" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK140" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>564</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -17096,17 +17010,15 @@
         <v>75</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" s="2"/>
       <c r="Q141" t="s" s="2">
         <v>75</v>
@@ -17131,11 +17043,11 @@
         <v>75</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z141" s="2"/>
       <c r="AA141" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="AB141" t="s" s="2">
         <v>75</v>
@@ -17153,7 +17065,7 @@
         <v>75</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>76</v>
@@ -17162,21 +17074,21 @@
         <v>83</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -17199,19 +17111,19 @@
         <v>75</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="P142" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="Q142" t="s" s="2">
         <v>75</v>
@@ -17236,11 +17148,11 @@
         <v>75</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z142" s="2"/>
       <c r="AA142" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="AB142" t="s" s="2">
         <v>75</v>
@@ -17258,7 +17170,7 @@
         <v>75</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>76</v>
@@ -17267,21 +17179,21 @@
         <v>83</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -17304,17 +17216,15 @@
         <v>75</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
         <v>75</v>
@@ -17363,7 +17273,7 @@
         <v>75</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>76</v>
@@ -17372,21 +17282,21 @@
         <v>83</v>
       </c>
       <c r="AJ143" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK143" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -17409,16 +17319,16 @@
         <v>75</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -17468,7 +17378,7 @@
         <v>75</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>76</v>
@@ -17477,10 +17387,10 @@
         <v>77</v>
       </c>
       <c r="AJ144" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK144" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T13:26:49+00:00</t>
+    <t>2024-09-23T13:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -589,7 +589,7 @@
 * Results from operations might involve resources that are not identified.</t>
   </si>
   <si>
-    <t>fullUrl might not be [unique in the context of a resource](bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
+    <t>fullUrl might not be [unique in the context of a resource](http://hl7.org/fhir/R4/bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
 Note that the fullUrl is not the same as the canonical URL - it's an absolute url for an endpoint serving the resource (these will happen to have the same value on the canonical server for the resource with the canonical URL).</t>
   </si>
   <si>
@@ -1039,7 +1039,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -1059,7 +1059,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1625,7 +1625,7 @@
     <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
   </si>
   <si>
-    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
   </si>
   <si>
     <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T13:29:51+00:00</t>
+    <t>2024-09-24T15:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T15:02:27+00:00</t>
+    <t>2024-09-25T14:04:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T14:04:17+00:00</t>
+    <t>2024-10-02T09:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
